--- a/artfynd/A 18263-2026 artfynd.xlsx
+++ b/artfynd/A 18263-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127464217</v>
+        <v>127597814</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>79795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>374</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gul dropplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cliostomum corrugatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504102</v>
+        <v>504264</v>
       </c>
       <c r="R2" t="n">
-        <v>6533184</v>
+        <v>6533030</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -780,11 +790,11 @@
         <v>127464157</v>
       </c>
       <c r="B3" t="n">
-        <v>92642</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -879,45 +889,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127464150</v>
+        <v>127464203</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gölamossen, NNV om, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504169</v>
+        <v>504094</v>
       </c>
       <c r="R4" t="n">
-        <v>6533112</v>
+        <v>6533142</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,14 +1000,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127464203</v>
+        <v>127464217</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1009,26 +1028,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gölamossen, NNV om, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504094</v>
+        <v>504102</v>
       </c>
       <c r="R5" t="n">
-        <v>6533142</v>
+        <v>6533184</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1105,7 @@
         <v>127464213</v>
       </c>
       <c r="B6" t="n">
-        <v>91372</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,6 +1201,414 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127464150</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gölamossen, NNV om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>504169</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6533112</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130649987</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jannebergsområdet, S Lerbäck, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>504029</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6533301</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Måreby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fågelinventering Vätternvatten 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127464027</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gölamossen, NNV om, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>504261</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6533084</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>skogsmosse</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127732572</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gölamossens N sida, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>504284</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6533020</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>mossekant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18263-2026 artfynd.xlsx
+++ b/artfynd/A 18263-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127597814</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464203</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464217</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464213</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464150</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
           <t>Fågelinventering Vätternvatten 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130649987</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127464027</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,8 +1654,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127732572</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>